--- a/artfynd/A 13556-2024 artfynd.xlsx
+++ b/artfynd/A 13556-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121701352</v>
+        <v>121700557</v>
       </c>
       <c r="B2" t="n">
-        <v>57363</v>
+        <v>5173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,51 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Armsjötorpet, Armsjötorpet, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627008</v>
+        <v>627082</v>
       </c>
       <c r="R2" t="n">
-        <v>6894560</v>
+        <v>6894263</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121700557</v>
+        <v>121701352</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>57363</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,46 +921,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Armsjötorpet, Armsjötorpet, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627082</v>
+        <v>627008</v>
       </c>
       <c r="R4" t="n">
-        <v>6894263</v>
+        <v>6894560</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 13556-2024 artfynd.xlsx
+++ b/artfynd/A 13556-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121700557</v>
+        <v>121700595</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>4770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627082</v>
+        <v>627083</v>
       </c>
       <c r="R2" t="n">
         <v>6894263</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121700941</v>
+        <v>121700557</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Armsjötorpet, Armsjötorpet, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627108</v>
+        <v>627082</v>
       </c>
       <c r="R3" t="n">
-        <v>6894419</v>
+        <v>6894263</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gick ej att räkna antalet pga snöläget.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121701352</v>
+        <v>121700403</v>
       </c>
       <c r="B4" t="n">
-        <v>57363</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,47 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627008</v>
+        <v>627111</v>
       </c>
       <c r="R4" t="n">
-        <v>6894560</v>
+        <v>6894318</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121700595</v>
+        <v>121700941</v>
       </c>
       <c r="B5" t="n">
-        <v>4770</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,43 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Armsjötorpet, Armsjötorpet, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627083</v>
+        <v>627108</v>
       </c>
       <c r="R5" t="n">
-        <v>6894263</v>
+        <v>6894419</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gick ej att räkna antalet pga snöläget.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121700403</v>
+        <v>121701352</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>57363</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,37 +1154,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627111</v>
+        <v>627008</v>
       </c>
       <c r="R6" t="n">
-        <v>6894318</v>
+        <v>6894560</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13556-2024 artfynd.xlsx
+++ b/artfynd/A 13556-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>121701352</v>
       </c>
       <c r="B6" t="n">
-        <v>57380</v>
+        <v>57385</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13556-2024 artfynd.xlsx
+++ b/artfynd/A 13556-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121700595</v>
+        <v>121700403</v>
       </c>
       <c r="B2" t="n">
-        <v>4770</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Armsjötorpet, Armsjötorpet, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627083</v>
+        <v>627111</v>
       </c>
       <c r="R2" t="n">
-        <v>6894263</v>
+        <v>6894318</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,58 +782,58 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121700557</v>
+        <v>121701352</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Armsjötorpet, Armsjötorpet, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627082</v>
+        <v>627008</v>
       </c>
       <c r="R3" t="n">
-        <v>6894263</v>
+        <v>6894560</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +899,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121700941</v>
+        <v>121701097</v>
       </c>
       <c r="B4" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627108</v>
+        <v>626983</v>
       </c>
       <c r="R4" t="n">
-        <v>6894419</v>
+        <v>6894591</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gick ej att räkna antalet pga snöläget.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,50 +1011,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121700403</v>
+        <v>121700595</v>
       </c>
       <c r="B5" t="n">
-        <v>90754</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Armsjötorpet, Armsjötorpet, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627111</v>
+        <v>627083</v>
       </c>
       <c r="R5" t="n">
-        <v>6894318</v>
+        <v>6894263</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,63 +1123,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121701352</v>
+        <v>121700557</v>
       </c>
       <c r="B6" t="n">
-        <v>57385</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Armsjötorpet, Armsjötorpet, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627008</v>
+        <v>627082</v>
       </c>
       <c r="R6" t="n">
-        <v>6894560</v>
+        <v>6894263</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,6 +1232,118 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121700941</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>627108</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6894419</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gick ej att räkna antalet pga snöläget.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13556-2024 artfynd.xlsx
+++ b/artfynd/A 13556-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121700403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121701352</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121701097</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121700595</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121700557</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,8 +1374,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121700941</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>